--- a/src/resources/data/PedagogyData.xlsx
+++ b/src/resources/data/PedagogyData.xlsx
@@ -1,27 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sowndariya\Desktop\Expleo\PLAYWRIGHT\Team5_Playwright\BDD_Playwright_Automation_Project\src\resources\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_ECBDF2EB95CFAE318A0E42449DC95162C5A1D8AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="1" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="AddElementData" sheetId="1" r:id="rId1"/>
-    <sheet name="SearchData" sheetId="2" r:id="rId2"/>
+    <sheet r:id="rId1" name="AddElementData" sheetId="1"/>
+    <sheet r:id="rId2" name="SearchData" sheetId="2"/>
   </sheets>
   <calcPr calcId="0" iterate="1" iterateCount="1000" iterateDelta="0.01"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>NewElementName</t>
   </si>
@@ -61,13 +76,21 @@
   <si>
     <t>You Do (Independent Practice)</t>
   </si>
+  <si>
+    <t>Lowercase Search</t>
+  </si>
+  <si>
+    <t>i do</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="1">
     <font>
+      <b val="0"/>
+      <i val="0"/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -91,25 +114,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -421,15 +437,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E85676BF-816E-49D4-B99D-5A66B7A95545}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{2B2CA1C2-5CDB-453C-9D8E-E9BFBC8A4746}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="7.796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="21.09765625" customWidth="1"/>
-    <col min="2" max="2" width="32.8984375" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15" defaultColWidth="7.75390625" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -437,7 +449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" ht="15" customHeight="1">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -446,26 +458,23 @@
       </c>
     </row>
   </sheetData>
+  <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
     <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
+  <extLst/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{275E1242-C44E-4C66-B136-13603CEF4519}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="7.796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="16.296875" customWidth="1"/>
-    <col min="2" max="2" width="15.296875" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{8F3F8C71-9AFD-4975-9FF3-228069479213}" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" defaultColWidth="7.75390625" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -476,7 +485,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" ht="15" customHeight="1">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -487,7 +496,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" ht="15" customHeight="1">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -498,7 +507,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -509,12 +518,25 @@
         <v>12</v>
       </c>
     </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
+  <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
     <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
+  <extLst/>
 </worksheet>
 </file>